--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>54867</x:v>
+        <x:v>50885</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54870</x:v>
+        <x:v>59002</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>50885</x:v>
+        <x:v>55508</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>59002</x:v>
+        <x:v>55511</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55508</x:v>
+        <x:v>57441</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>55511</x:v>
+        <x:v>57447</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -1104,7 +1104,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1163,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1443,7 +1443,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>58</x:v>
@@ -1499,7 +1499,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>48</x:v>
@@ -1608,7 +1608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>57441</x:v>
+        <x:v>58677</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1720,7 +1720,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1888,7 +1888,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1944,7 +1944,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P17" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="Q17" s="0">
         <x:v>4000</x:v>
@@ -2059,7 +2059,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q19" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="R19" s="3" t="s">
         <x:v>58</x:v>
@@ -2115,7 +2115,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
         <x:v>48</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>57447</x:v>
+        <x:v>57654</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -164,7 +164,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -179,43 +182,16 @@
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
-    <x:t>Connection acknowledged (ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>Client sending data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sabc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S111</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -242,22 +218,12 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -284,7 +250,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -294,14 +260,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -311,14 +271,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -992,7 +944,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1089,28 +1041,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1130,10 +1082,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1145,28 +1097,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1186,10 +1138,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1201,28 +1153,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1257,28 +1209,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="P5" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1298,10 +1250,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1313,28 +1265,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1369,7 +1321,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1389,8 +1341,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1410,10 +1362,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1425,28 +1377,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1466,10 +1418,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1481,28 +1433,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R9" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1522,10 +1474,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1537,28 +1489,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>58677</x:v>
+      <x:c r="P10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1578,10 +1530,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1593,28 +1545,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="0">
-        <x:v>58677</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R11" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1634,10 +1586,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1649,7 +1601,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1669,8 +1621,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="R12" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1705,28 +1657,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:18">
@@ -1746,10 +1698,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>17</x:v>
@@ -1761,28 +1713,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R14" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q14" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="R14" s="2" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1802,10 +1754,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1817,28 +1769,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P15" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="Q15" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q15" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
@@ -1873,28 +1825,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="P16" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="Q16" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q16" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1914,10 +1866,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1929,28 +1881,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P17" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="Q17" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R17" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1985,7 +1937,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -2005,8 +1957,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="R18" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2026,10 +1978,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -2041,28 +1993,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P19" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q19" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R19" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2082,10 +2034,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2097,28 +2049,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P20" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q20" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R20" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2138,10 +2090,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2153,28 +2105,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q21" s="0">
-        <x:v>57654</x:v>
+      <x:c r="P21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2194,10 +2146,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2209,28 +2161,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="0">
-        <x:v>57654</x:v>
-      </x:c>
-      <x:c r="Q22" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R22" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2250,10 +2202,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
@@ -2265,7 +2217,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2285,8 +2237,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>60</x:v>
+      <x:c r="R23" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC6/GradeDetail.xlsx
@@ -164,18 +164,24 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -192,6 +198,18 @@
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +236,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,7 +245,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -250,7 +278,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -260,8 +288,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -271,6 +305,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -930,11 +972,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R23"/>
+  <x:dimension ref="A1:R34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1041,25 +1083,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>49</x:v>
@@ -1097,7 +1139,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1117,8 +1159,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R3" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1138,43 +1180,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R4" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1194,10 +1236,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1209,7 +1251,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1229,8 +1271,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R5" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1250,43 +1292,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="L6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1306,10 +1348,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1321,7 +1363,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1341,8 +1383,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R7" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1362,43 +1404,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1418,10 +1460,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,7 +1475,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1453,8 +1495,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R9" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1474,43 +1516,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="L10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R10" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1530,10 +1572,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1545,7 +1587,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1565,8 +1607,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R11" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1586,43 +1628,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G12" s="0" t="s">
+      <x:c r="L12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1657,25 +1699,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q13" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P13" s="0">
+        <x:v>56730</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
         <x:v>49</x:v>
@@ -1713,7 +1755,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
         <x:v>17</x:v>
@@ -1733,8 +1775,8 @@
       <x:c r="Q14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R14" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R14" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1754,43 +1796,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
+      <x:c r="L15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R15" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R15" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
@@ -1810,10 +1852,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>17</x:v>
@@ -1825,7 +1867,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
         <x:v>17</x:v>
@@ -1845,8 +1887,8 @@
       <x:c r="Q16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R16" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R16" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1866,43 +1908,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G17" s="0" t="s">
+      <x:c r="L17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R17" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I17" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J17" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K17" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R17" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1922,10 +1964,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
         <x:v>17</x:v>
@@ -1937,7 +1979,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -1957,8 +1999,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R18" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -1978,43 +2020,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G19" s="0" t="s">
+      <x:c r="L19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R19" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I19" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K19" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q19" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R19" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2034,10 +2076,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2049,7 +2091,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
         <x:v>17</x:v>
@@ -2069,8 +2111,8 @@
       <x:c r="Q20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R20" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R20" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2090,43 +2132,43 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J21" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K21" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G21" s="0" t="s">
+      <x:c r="L21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R21" s="3" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="H21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="J21" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="K21" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q21" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R21" s="2" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2146,10 +2188,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2161,7 +2203,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>17</x:v>
@@ -2181,8 +2223,8 @@
       <x:c r="Q22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R22" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="R22" s="3" t="s">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2202,43 +2244,659 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G23" s="0" t="s">
+      <x:c r="L23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="H23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="J23" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="K23" s="0" t="s">
+    </x:row>
+    <x:row r="24" spans="1:18">
+      <x:c r="A24" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P24" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q24" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="R24" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:18">
+      <x:c r="A25" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="L23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q23" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R23" s="2" t="s">
-        <x:v>49</x:v>
+      <x:c r="M25" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O25" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P25" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="Q25" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R25" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:18">
+      <x:c r="A26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L26" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M26" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N26" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O26" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P26" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q26" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="R26" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:18">
+      <x:c r="A27" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L27" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M27" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N27" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O27" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P27" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q27" s="0">
+        <x:v>45850</x:v>
+      </x:c>
+      <x:c r="R27" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:18">
+      <x:c r="A28" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K28" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L28" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M28" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N28" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P28" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="Q28" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R28" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:18">
+      <x:c r="A29" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K29" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L29" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M29" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N29" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O29" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P29" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q29" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="R29" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:18">
+      <x:c r="A30" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K30" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L30" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M30" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N30" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O30" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P30" s="0">
+        <x:v>47324</x:v>
+      </x:c>
+      <x:c r="Q30" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R30" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:18">
+      <x:c r="A31" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K31" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L31" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M31" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N31" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O31" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P31" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q31" s="0">
+        <x:v>47324</x:v>
+      </x:c>
+      <x:c r="R31" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:18">
+      <x:c r="A32" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K32" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="L32" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="M32" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N32" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="O32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P32" s="0">
+        <x:v>53122</x:v>
+      </x:c>
+      <x:c r="Q32" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R32" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:18">
+      <x:c r="A33" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K33" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L33" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M33" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N33" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O33" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P33" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q33" s="0">
+        <x:v>53122</x:v>
+      </x:c>
+      <x:c r="R33" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:18">
+      <x:c r="A34" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K34" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L34" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M34" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="N34" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="O34" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P34" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q34" s="0">
+        <x:v>56730</x:v>
+      </x:c>
+      <x:c r="R34" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
